--- a/Raw Data/Stock and Production/MPOB Exports 3Y.xlsx
+++ b/Raw Data/Stock and Production/MPOB Exports 3Y.xlsx
@@ -1,42 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ClaudeCode\Raw Data\Stock and Production\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3E61AA-C7AA-4EEB-96AD-D7DE4CA8F57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="41130" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Table Data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>MYPOME-PO (COMM_LAST)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="dd/M/yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/m/yyyy;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,14 +71,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,328 +411,338 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="2" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>MYPOME-PO (COMM_LAST)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v>Close</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="d">
-        <v>2026-01-01T00:00:00.000Z</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46054</v>
       </c>
       <c r="B3">
-        <v>1484267</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="d">
-        <v>2025-12-01T00:00:00.000Z</v>
+        <v>1127605</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46023</v>
       </c>
       <c r="B4">
+        <v>1454625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B5">
         <v>1331894</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="d">
-        <v>2025-11-01T00:00:00.000Z</v>
-      </c>
-      <c r="B5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B6">
         <v>1213130</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="d">
-        <v>2025-10-01T00:00:00.000Z</v>
-      </c>
-      <c r="B6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B7">
         <v>1687495</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="d">
-        <v>2025-09-01T00:00:00.000Z</v>
-      </c>
-      <c r="B7">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B8">
         <v>1427609</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="d">
-        <v>2025-08-01T00:00:00.000Z</v>
-      </c>
-      <c r="B8">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B9">
         <v>1325672</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="d">
-        <v>2025-07-01T00:00:00.000Z</v>
-      </c>
-      <c r="B9">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B10">
         <v>1328547</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="d">
-        <v>2025-06-01T00:00:00.000Z</v>
-      </c>
-      <c r="B10">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B11">
         <v>1260930</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="d">
-        <v>2025-05-01T00:00:00.000Z</v>
-      </c>
-      <c r="B11">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B12">
         <v>1407411</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="d">
-        <v>2025-04-01T00:00:00.000Z</v>
-      </c>
-      <c r="B12">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B13">
         <v>1104333</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="d">
-        <v>2025-03-01T00:00:00.000Z</v>
-      </c>
-      <c r="B13">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45717</v>
+      </c>
+      <c r="B14">
         <v>1005547</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="d">
-        <v>2025-02-01T00:00:00.000Z</v>
-      </c>
-      <c r="B14">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45689</v>
+      </c>
+      <c r="B15">
         <v>996460</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="d">
-        <v>2025-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="B15">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45658</v>
+      </c>
+      <c r="B16">
         <v>1196849</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="d">
-        <v>2024-12-01T00:00:00.000Z</v>
-      </c>
-      <c r="B16">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45627</v>
+      </c>
+      <c r="B17">
         <v>1341936</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="d">
-        <v>2024-11-01T00:00:00.000Z</v>
-      </c>
-      <c r="B17">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>45597</v>
+      </c>
+      <c r="B18">
         <v>1490293</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="d">
-        <v>2024-10-01T00:00:00.000Z</v>
-      </c>
-      <c r="B18">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>45566</v>
+      </c>
+      <c r="B19">
         <v>1744265</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="d">
-        <v>2024-09-01T00:00:00.000Z</v>
-      </c>
-      <c r="B19">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>45536</v>
+      </c>
+      <c r="B20">
         <v>1559846</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="d">
-        <v>2024-08-01T00:00:00.000Z</v>
-      </c>
-      <c r="B20">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>45505</v>
+      </c>
+      <c r="B21">
         <v>1528632</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="d">
-        <v>2024-07-01T00:00:00.000Z</v>
-      </c>
-      <c r="B21">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>45474</v>
+      </c>
+      <c r="B22">
         <v>1689710</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="d">
-        <v>2024-06-01T00:00:00.000Z</v>
-      </c>
-      <c r="B22">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>45444</v>
+      </c>
+      <c r="B23">
         <v>1207414</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="d">
-        <v>2024-05-01T00:00:00.000Z</v>
-      </c>
-      <c r="B23">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>45413</v>
+      </c>
+      <c r="B24">
         <v>1382429</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="d">
-        <v>2024-04-01T00:00:00.000Z</v>
-      </c>
-      <c r="B24">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>45383</v>
+      </c>
+      <c r="B25">
         <v>1234208</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="d">
-        <v>2024-03-01T00:00:00.000Z</v>
-      </c>
-      <c r="B25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>45352</v>
+      </c>
+      <c r="B26">
         <v>1317628</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="d">
-        <v>2024-02-01T00:00:00.000Z</v>
-      </c>
-      <c r="B26">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>45323</v>
+      </c>
+      <c r="B27">
         <v>1015537</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="d">
-        <v>2024-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="B27">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>45292</v>
+      </c>
+      <c r="B28">
         <v>1350574</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="d">
-        <v>2023-12-01T00:00:00.000Z</v>
-      </c>
-      <c r="B28">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>45261</v>
+      </c>
+      <c r="B29">
         <v>1334441</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="d">
-        <v>2023-11-01T00:00:00.000Z</v>
-      </c>
-      <c r="B29">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>45231</v>
+      </c>
+      <c r="B30">
         <v>1396721</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="d">
-        <v>2023-10-01T00:00:00.000Z</v>
-      </c>
-      <c r="B30">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>45200</v>
+      </c>
+      <c r="B31">
         <v>1466065</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="d">
-        <v>2023-09-01T00:00:00.000Z</v>
-      </c>
-      <c r="B31">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>45170</v>
+      </c>
+      <c r="B32">
         <v>1196113</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="d">
-        <v>2023-08-01T00:00:00.000Z</v>
-      </c>
-      <c r="B32">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>45139</v>
+      </c>
+      <c r="B33">
         <v>1221848</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="d">
-        <v>2023-07-01T00:00:00.000Z</v>
-      </c>
-      <c r="B33">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>45108</v>
+      </c>
+      <c r="B34">
         <v>1354336</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="d">
-        <v>2023-06-01T00:00:00.000Z</v>
-      </c>
-      <c r="B34">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>45078</v>
+      </c>
+      <c r="B35">
         <v>1171741</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="d">
-        <v>2023-05-01T00:00:00.000Z</v>
-      </c>
-      <c r="B35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>45047</v>
+      </c>
+      <c r="B36">
         <v>1079020</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="d">
-        <v>2023-04-01T00:00:00.000Z</v>
-      </c>
-      <c r="B36">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>45017</v>
+      </c>
+      <c r="B37">
         <v>1087541</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="d">
-        <v>2023-03-01T00:00:00.000Z</v>
-      </c>
-      <c r="B37">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>44986</v>
+      </c>
+      <c r="B38">
         <v>1487836</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="d">
-        <v>2023-02-01T00:00:00.000Z</v>
-      </c>
-      <c r="B38">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B39">
         <v>1127953</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="d">
-        <v>2023-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="B39">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>44927</v>
+      </c>
+      <c r="B40">
         <v>1137005</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B39"/>
+    <ignoredError sqref="A5:B40 A1:B2 A4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>